--- a/data/data_raw/eurostat/AT_coal_en_bal_nrg_bal_c.xlsx
+++ b/data/data_raw/eurostat/AT_coal_en_bal_nrg_bal_c.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN140"/>
+  <dimension ref="A1:AO140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +624,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -754,6 +759,9 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,6 +896,9 @@
       <c r="AN3" t="n">
         <v>0</v>
       </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1015,10 +1026,13 @@
         <v>29998.895</v>
       </c>
       <c r="AM4" t="n">
-        <v>29248.446</v>
+        <v>29248.445</v>
       </c>
       <c r="AN4" t="n">
-        <v>28892.276</v>
+        <v>28892.277</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>27576.209</v>
       </c>
     </row>
     <row r="5">
@@ -1141,16 +1155,19 @@
         <v>387.222</v>
       </c>
       <c r="AK5" t="n">
-        <v>304.602</v>
+        <v>304.601</v>
       </c>
       <c r="AL5" t="n">
         <v>452.424</v>
       </c>
       <c r="AM5" t="n">
-        <v>414.724</v>
+        <v>414.725</v>
       </c>
       <c r="AN5" t="n">
         <v>384.521</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>500.235</v>
       </c>
     </row>
     <row r="6">
@@ -1273,16 +1290,19 @@
         <v>1120.218</v>
       </c>
       <c r="AK6" t="n">
-        <v>630.446</v>
+        <v>630.439</v>
       </c>
       <c r="AL6" t="n">
-        <v>174.796</v>
+        <v>174.793</v>
       </c>
       <c r="AM6" t="n">
         <v>27.475</v>
       </c>
       <c r="AN6" t="n">
-        <v>-563.1900000000001</v>
+        <v>-563.175</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>151.162</v>
       </c>
     </row>
     <row r="7">
@@ -1405,16 +1425,19 @@
         <v>33553.374</v>
       </c>
       <c r="AK7" t="n">
-        <v>28743.606</v>
+        <v>28743.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>29721.268</v>
+        <v>29721.264</v>
       </c>
       <c r="AM7" t="n">
         <v>28861.196</v>
       </c>
       <c r="AN7" t="n">
-        <v>27944.566</v>
+        <v>27944.581</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>27227.136</v>
       </c>
     </row>
     <row r="8">
@@ -1548,6 +1571,9 @@
       <c r="AN8" t="n">
         <v>0</v>
       </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1669,16 +1695,19 @@
         <v>33553.374</v>
       </c>
       <c r="AK9" t="n">
-        <v>28743.606</v>
+        <v>28743.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>29721.268</v>
+        <v>29721.264</v>
       </c>
       <c r="AM9" t="n">
         <v>28861.196</v>
       </c>
       <c r="AN9" t="n">
-        <v>27944.566</v>
+        <v>27944.581</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>27227.136</v>
       </c>
     </row>
     <row r="10">
@@ -1744,6 +1773,7 @@
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1865,16 +1895,19 @@
         <v>33553.374</v>
       </c>
       <c r="AK11" t="n">
-        <v>28743.606</v>
+        <v>28743.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>29721.268</v>
+        <v>29721.264</v>
       </c>
       <c r="AM11" t="n">
         <v>28861.196</v>
       </c>
       <c r="AN11" t="n">
-        <v>27944.566</v>
+        <v>27944.581</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>27227.136</v>
       </c>
     </row>
     <row r="12">
@@ -1940,6 +1973,7 @@
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2004,6 +2038,7 @@
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2068,6 +2103,7 @@
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2189,16 +2225,19 @@
         <v>40587.789</v>
       </c>
       <c r="AK15" t="n">
-        <v>35375.017</v>
+        <v>35375.015</v>
       </c>
       <c r="AL15" t="n">
-        <v>37352.146</v>
+        <v>37352.147</v>
       </c>
       <c r="AM15" t="n">
-        <v>36113.443</v>
+        <v>36113.45</v>
       </c>
       <c r="AN15" t="n">
-        <v>35644.945</v>
+        <v>35644.954</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>34628.999</v>
       </c>
     </row>
     <row r="16">
@@ -2321,16 +2360,19 @@
         <v>4264.508</v>
       </c>
       <c r="AK16" t="n">
-        <v>1507.587</v>
+        <v>1507.585</v>
       </c>
       <c r="AL16" t="n">
-        <v>268.56</v>
+        <v>268.561</v>
       </c>
       <c r="AM16" t="n">
-        <v>93.813</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AN16" t="n">
-        <v>25.922</v>
+        <v>25.931</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>37.388</v>
       </c>
     </row>
     <row r="17">
@@ -2464,6 +2506,9 @@
       <c r="AN17" t="n">
         <v>0</v>
       </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2596,6 +2641,9 @@
       <c r="AN18" t="n">
         <v>0</v>
       </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2728,6 +2776,9 @@
       <c r="AN19" t="n">
         <v>0</v>
       </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2860,6 +2911,9 @@
       <c r="AN20" t="n">
         <v>0</v>
       </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2981,16 +3035,19 @@
         <v>324.551</v>
       </c>
       <c r="AK21" t="n">
-        <v>307.702</v>
+        <v>307.7</v>
       </c>
       <c r="AL21" t="n">
-        <v>247.726</v>
+        <v>247.727</v>
       </c>
       <c r="AM21" t="n">
-        <v>93.407</v>
+        <v>93.413</v>
       </c>
       <c r="AN21" t="n">
-        <v>25.922</v>
+        <v>25.931</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>37.388</v>
       </c>
     </row>
     <row r="22">
@@ -3122,6 +3179,9 @@
         <v>0</v>
       </c>
       <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3188,6 +3248,7 @@
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3252,6 +3313,7 @@
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3316,6 +3378,7 @@
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3380,6 +3443,7 @@
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -3444,6 +3508,7 @@
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -3576,6 +3641,9 @@
       <c r="AN28" t="n">
         <v>14352.067</v>
       </c>
+      <c r="AO28" t="n">
+        <v>14832.762</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3700,13 +3768,16 @@
         <v>19809.787</v>
       </c>
       <c r="AL29" t="n">
-        <v>22929.862</v>
+        <v>22929.861</v>
       </c>
       <c r="AM29" t="n">
         <v>21719.127</v>
       </c>
       <c r="AN29" t="n">
         <v>21266.956</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>19758.848</v>
       </c>
     </row>
     <row r="30">
@@ -3838,6 +3909,9 @@
         <v>0</v>
       </c>
       <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3904,6 +3978,7 @@
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3968,6 +4043,7 @@
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -4032,6 +4108,7 @@
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -4096,6 +4173,7 @@
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -4160,6 +4238,7 @@
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -4224,6 +4303,7 @@
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -4288,6 +4368,7 @@
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -4420,6 +4501,9 @@
       <c r="AN38" t="n">
         <v>0</v>
       </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -4552,6 +4636,9 @@
       <c r="AN39" t="n">
         <v>0</v>
       </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -4682,6 +4769,9 @@
         <v>0</v>
       </c>
       <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4748,6 +4838,7 @@
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -4812,6 +4903,7 @@
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4876,6 +4968,7 @@
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4940,6 +5033,7 @@
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -5072,6 +5166,9 @@
       <c r="AN45" t="n">
         <v>0</v>
       </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -5203,6 +5300,9 @@
       </c>
       <c r="AN46" t="n">
         <v>10704.919</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>10443.832</v>
       </c>
     </row>
     <row r="47">
@@ -5268,6 +5368,7 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -5332,6 +5433,7 @@
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -5396,6 +5498,7 @@
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -5460,6 +5563,7 @@
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -5524,6 +5628,7 @@
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -5588,6 +5693,7 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr"/>
       <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -5652,6 +5758,7 @@
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5716,6 +5823,7 @@
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5780,6 +5888,7 @@
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5844,6 +5953,7 @@
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5908,6 +6018,7 @@
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -6040,6 +6151,9 @@
       <c r="AN58" t="n">
         <v>10704.919</v>
       </c>
+      <c r="AO58" t="n">
+        <v>10443.832</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -6172,6 +6286,9 @@
       <c r="AN59" t="n">
         <v>0</v>
       </c>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -6302,6 +6419,9 @@
         <v>0</v>
       </c>
       <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6368,6 +6488,7 @@
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6432,6 +6553,7 @@
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -6496,6 +6618,7 @@
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr"/>
       <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -6560,6 +6683,7 @@
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr"/>
       <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -6624,6 +6748,7 @@
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -6688,6 +6813,7 @@
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr"/>
       <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -6752,6 +6878,7 @@
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -6884,6 +7011,9 @@
       <c r="AN68" t="n">
         <v>0</v>
       </c>
+      <c r="AO68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -7014,6 +7144,9 @@
         <v>0</v>
       </c>
       <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7080,6 +7213,7 @@
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr"/>
       <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -7144,6 +7278,7 @@
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr"/>
       <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -7208,6 +7343,7 @@
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr"/>
       <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -7272,6 +7408,7 @@
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr"/>
       <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -7336,6 +7473,7 @@
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr"/>
       <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -7468,6 +7606,9 @@
       <c r="AN75" t="n">
         <v>0</v>
       </c>
+      <c r="AO75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -7600,6 +7741,9 @@
       <c r="AN76" t="n">
         <v>114.246</v>
       </c>
+      <c r="AO76" t="n">
+        <v>50.719</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -7732,6 +7876,9 @@
       <c r="AN77" t="n">
         <v>0</v>
       </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -7862,6 +8009,9 @@
         <v>0</v>
       </c>
       <c r="AN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7928,6 +8078,7 @@
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr"/>
       <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -8060,6 +8211,9 @@
       <c r="AN80" t="n">
         <v>0</v>
       </c>
+      <c r="AO80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -8192,6 +8346,9 @@
       <c r="AN81" t="n">
         <v>0</v>
       </c>
+      <c r="AO81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -8324,6 +8481,9 @@
       <c r="AN82" t="n">
         <v>0</v>
       </c>
+      <c r="AO82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -8456,6 +8616,9 @@
       <c r="AN83" t="n">
         <v>0</v>
       </c>
+      <c r="AO83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -8588,6 +8751,9 @@
       <c r="AN84" t="n">
         <v>114.246</v>
       </c>
+      <c r="AO84" t="n">
+        <v>50.719</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -8718,6 +8884,9 @@
         <v>0</v>
       </c>
       <c r="AN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8784,6 +8953,7 @@
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
       <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -8914,6 +9084,9 @@
         <v>0</v>
       </c>
       <c r="AN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8980,6 +9153,7 @@
       <c r="AL88" t="inlineStr"/>
       <c r="AM88" t="inlineStr"/>
       <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -9044,6 +9218,7 @@
       <c r="AL89" t="inlineStr"/>
       <c r="AM89" t="inlineStr"/>
       <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -9108,6 +9283,7 @@
       <c r="AL90" t="inlineStr"/>
       <c r="AM90" t="inlineStr"/>
       <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -9172,6 +9348,7 @@
       <c r="AL91" t="inlineStr"/>
       <c r="AM91" t="inlineStr"/>
       <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -9304,6 +9481,9 @@
       <c r="AN92" t="n">
         <v>0</v>
       </c>
+      <c r="AO92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -9436,6 +9616,9 @@
       <c r="AN93" t="n">
         <v>0</v>
       </c>
+      <c r="AO93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -9557,16 +9740,19 @@
         <v>3900.608</v>
       </c>
       <c r="AK94" t="n">
-        <v>4261.574</v>
+        <v>4261.57</v>
       </c>
       <c r="AL94" t="n">
-        <v>3252.064</v>
+        <v>3252.06</v>
       </c>
       <c r="AM94" t="n">
-        <v>3163.133</v>
+        <v>3163.126</v>
       </c>
       <c r="AN94" t="n">
-        <v>2890.294</v>
+        <v>2890.301</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>2991.25</v>
       </c>
     </row>
     <row r="95">
@@ -9689,16 +9875,19 @@
         <v>310.767</v>
       </c>
       <c r="AK95" t="n">
-        <v>260.931</v>
+        <v>260.932</v>
       </c>
       <c r="AL95" t="n">
-        <v>458.673</v>
+        <v>458.681</v>
       </c>
       <c r="AM95" t="n">
         <v>326.191</v>
       </c>
       <c r="AN95" t="n">
-        <v>247.889</v>
+        <v>247.888</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>393.452</v>
       </c>
     </row>
     <row r="96">
@@ -9821,16 +10010,19 @@
         <v>310.767</v>
       </c>
       <c r="AK96" t="n">
-        <v>260.931</v>
+        <v>260.932</v>
       </c>
       <c r="AL96" t="n">
-        <v>458.673</v>
+        <v>458.681</v>
       </c>
       <c r="AM96" t="n">
         <v>326.191</v>
       </c>
       <c r="AN96" t="n">
-        <v>247.889</v>
+        <v>247.888</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>393.452</v>
       </c>
     </row>
     <row r="97">
@@ -9896,6 +10088,7 @@
       <c r="AL97" t="inlineStr"/>
       <c r="AM97" t="inlineStr"/>
       <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -9960,6 +10153,7 @@
       <c r="AL98" t="inlineStr"/>
       <c r="AM98" t="inlineStr"/>
       <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -10024,6 +10218,7 @@
       <c r="AL99" t="inlineStr"/>
       <c r="AM99" t="inlineStr"/>
       <c r="AN99" t="inlineStr"/>
+      <c r="AO99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -10156,6 +10351,9 @@
       <c r="AN100" t="n">
         <v>0</v>
       </c>
+      <c r="AO100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -10288,6 +10486,9 @@
       <c r="AN101" t="n">
         <v>0</v>
       </c>
+      <c r="AO101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -10409,16 +10610,19 @@
         <v>3589.84</v>
       </c>
       <c r="AK102" t="n">
-        <v>3998.47</v>
+        <v>4000.594</v>
       </c>
       <c r="AL102" t="n">
-        <v>2793.374</v>
+        <v>2791.459</v>
       </c>
       <c r="AM102" t="n">
-        <v>2836.929</v>
+        <v>2836.886</v>
       </c>
       <c r="AN102" t="n">
-        <v>2642.348</v>
+        <v>2642.355</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>2597.812</v>
       </c>
     </row>
     <row r="103">
@@ -10541,16 +10745,19 @@
         <v>3354.234</v>
       </c>
       <c r="AK103" t="n">
-        <v>3834.85</v>
+        <v>3836.786</v>
       </c>
       <c r="AL103" t="n">
-        <v>2675.967</v>
+        <v>2673.545</v>
       </c>
       <c r="AM103" t="n">
-        <v>2736.378</v>
+        <v>2736.38</v>
       </c>
       <c r="AN103" t="n">
-        <v>2553.608</v>
+        <v>2565.611</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>2551.103</v>
       </c>
     </row>
     <row r="104">
@@ -10673,16 +10880,19 @@
         <v>1885.541</v>
       </c>
       <c r="AK104" t="n">
-        <v>1973.034</v>
+        <v>1973.033</v>
       </c>
       <c r="AL104" t="n">
-        <v>1073.161</v>
+        <v>1072.815</v>
       </c>
       <c r="AM104" t="n">
-        <v>1564.316</v>
+        <v>1564.379</v>
       </c>
       <c r="AN104" t="n">
-        <v>1919.795</v>
+        <v>1931.006</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>1850.728</v>
       </c>
     </row>
     <row r="105">
@@ -10808,13 +11018,16 @@
         <v>93.878</v>
       </c>
       <c r="AL105" t="n">
-        <v>96.874</v>
+        <v>96.85899999999999</v>
       </c>
       <c r="AM105" t="n">
         <v>116.234</v>
       </c>
       <c r="AN105" t="n">
-        <v>36.306</v>
+        <v>37.828</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>61.674</v>
       </c>
     </row>
     <row r="106">
@@ -10937,7 +11150,7 @@
         <v>35.271</v>
       </c>
       <c r="AK106" t="n">
-        <v>34.698</v>
+        <v>34.697</v>
       </c>
       <c r="AL106" t="n">
         <v>14.634</v>
@@ -10946,7 +11159,10 @@
         <v>31.703</v>
       </c>
       <c r="AN106" t="n">
-        <v>39.152</v>
+        <v>39.437</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>42.316</v>
       </c>
     </row>
     <row r="107">
@@ -11069,16 +11285,19 @@
         <v>651.851</v>
       </c>
       <c r="AK107" t="n">
-        <v>1030.332</v>
+        <v>1030.274</v>
       </c>
       <c r="AL107" t="n">
-        <v>731.5</v>
+        <v>729.527</v>
       </c>
       <c r="AM107" t="n">
-        <v>633.701</v>
+        <v>633.648</v>
       </c>
       <c r="AN107" t="n">
-        <v>373.409</v>
+        <v>372.11</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>270.718</v>
       </c>
     </row>
     <row r="108">
@@ -11212,6 +11431,9 @@
       <c r="AN108" t="n">
         <v>0</v>
       </c>
+      <c r="AO108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -11344,6 +11566,9 @@
       <c r="AN109" t="n">
         <v>0</v>
       </c>
+      <c r="AO109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -11476,6 +11701,9 @@
       <c r="AN110" t="n">
         <v>0</v>
       </c>
+      <c r="AO110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -11600,13 +11828,16 @@
         <v>32.511</v>
       </c>
       <c r="AL111" t="n">
-        <v>19.341</v>
+        <v>19.333</v>
       </c>
       <c r="AM111" t="n">
         <v>40.706</v>
       </c>
       <c r="AN111" t="n">
-        <v>44.06</v>
+        <v>44.314</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>72.069</v>
       </c>
     </row>
     <row r="112">
@@ -11729,16 +11960,19 @@
         <v>710.37</v>
       </c>
       <c r="AK112" t="n">
-        <v>668.546</v>
+        <v>668.362</v>
       </c>
       <c r="AL112" t="n">
-        <v>740.457</v>
+        <v>740.378</v>
       </c>
       <c r="AM112" t="n">
-        <v>349.717</v>
+        <v>349.709</v>
       </c>
       <c r="AN112" t="n">
-        <v>140.886</v>
+        <v>140.917</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>253.598</v>
       </c>
     </row>
     <row r="113">
@@ -11872,6 +12106,9 @@
       <c r="AN113" t="n">
         <v>0</v>
       </c>
+      <c r="AO113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -12004,6 +12241,9 @@
       <c r="AN114" t="n">
         <v>0</v>
       </c>
+      <c r="AO114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -12136,6 +12376,9 @@
       <c r="AN115" t="n">
         <v>0</v>
       </c>
+      <c r="AO115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -12257,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="AK116" t="n">
-        <v>0</v>
+        <v>2.179</v>
       </c>
       <c r="AL116" t="n">
         <v>0</v>
@@ -12266,6 +12509,9 @@
         <v>0</v>
       </c>
       <c r="AN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12400,6 +12646,9 @@
       <c r="AN117" t="n">
         <v>0.799</v>
       </c>
+      <c r="AO117" t="n">
+        <v>0.704</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -12531,6 +12780,9 @@
       </c>
       <c r="AN118" t="n">
         <v>0.799</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.704</v>
       </c>
     </row>
     <row r="119">
@@ -12596,6 +12848,7 @@
       <c r="AL119" t="inlineStr"/>
       <c r="AM119" t="inlineStr"/>
       <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -12660,6 +12913,7 @@
       <c r="AL120" t="inlineStr"/>
       <c r="AM120" t="inlineStr"/>
       <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -12790,6 +13044,9 @@
         <v>0</v>
       </c>
       <c r="AN121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12856,6 +13113,7 @@
       <c r="AL122" t="inlineStr"/>
       <c r="AM122" t="inlineStr"/>
       <c r="AN122" t="inlineStr"/>
+      <c r="AO122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -12988,6 +13246,9 @@
       <c r="AN123" t="n">
         <v>0</v>
       </c>
+      <c r="AO123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -13109,16 +13370,19 @@
         <v>234.411</v>
       </c>
       <c r="AK124" t="n">
-        <v>162.529</v>
+        <v>162.717</v>
       </c>
       <c r="AL124" t="n">
-        <v>116.342</v>
+        <v>116.85</v>
       </c>
       <c r="AM124" t="n">
-        <v>99.56399999999999</v>
+        <v>99.51900000000001</v>
       </c>
       <c r="AN124" t="n">
-        <v>87.941</v>
+        <v>75.94499999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>46.005</v>
       </c>
     </row>
     <row r="125">
@@ -13252,6 +13516,9 @@
       <c r="AN125" t="n">
         <v>0</v>
       </c>
+      <c r="AO125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -13373,16 +13640,19 @@
         <v>229.497</v>
       </c>
       <c r="AK126" t="n">
-        <v>157.668</v>
+        <v>157.852</v>
       </c>
       <c r="AL126" t="n">
-        <v>112.844</v>
+        <v>107.985</v>
       </c>
       <c r="AM126" t="n">
-        <v>96.876</v>
+        <v>96.88500000000001</v>
       </c>
       <c r="AN126" t="n">
-        <v>85.732</v>
+        <v>74.05800000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>44.977</v>
       </c>
     </row>
     <row r="127">
@@ -13505,16 +13775,19 @@
         <v>4.914</v>
       </c>
       <c r="AK127" t="n">
-        <v>4.862</v>
+        <v>4.851</v>
       </c>
       <c r="AL127" t="n">
-        <v>3.487</v>
+        <v>8.843</v>
       </c>
       <c r="AM127" t="n">
-        <v>2.683</v>
+        <v>2.629</v>
       </c>
       <c r="AN127" t="n">
-        <v>2.204</v>
+        <v>1.881</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.028</v>
       </c>
     </row>
     <row r="128">
@@ -13637,16 +13910,19 @@
         <v>0</v>
       </c>
       <c r="AK128" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AL128" t="n">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="AM128" t="n">
         <v>0.006</v>
       </c>
       <c r="AN128" t="n">
         <v>0.006</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -13780,6 +14056,9 @@
       <c r="AN129" t="n">
         <v>0</v>
       </c>
+      <c r="AO129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -13901,16 +14180,19 @@
         <v>0.002</v>
       </c>
       <c r="AK130" t="n">
-        <v>2.173</v>
+        <v>0.044</v>
       </c>
       <c r="AL130" t="n">
-        <v>0.017</v>
+        <v>1.92</v>
       </c>
       <c r="AM130" t="n">
-        <v>0.013</v>
+        <v>0.049</v>
       </c>
       <c r="AN130" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>-0.014</v>
       </c>
     </row>
     <row r="131">
@@ -14044,6 +14326,9 @@
       <c r="AN131" t="n">
         <v>20.937</v>
       </c>
+      <c r="AO131" t="n">
+        <v>23.648</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -14176,6 +14461,9 @@
       <c r="AN132" t="n">
         <v>0</v>
       </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -14308,6 +14596,9 @@
       <c r="AN133" t="n">
         <v>0</v>
       </c>
+      <c r="AO133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -14440,6 +14731,9 @@
       <c r="AN134" t="n">
         <v>0</v>
       </c>
+      <c r="AO134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -14572,6 +14866,9 @@
       <c r="AN135" t="n">
         <v>20.937</v>
       </c>
+      <c r="AO135" t="n">
+        <v>23.648</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -14704,6 +15001,9 @@
       <c r="AN136" t="n">
         <v>0</v>
       </c>
+      <c r="AO136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -14836,6 +15136,9 @@
       <c r="AN137" t="n">
         <v>0</v>
       </c>
+      <c r="AO137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -14968,6 +15271,9 @@
       <c r="AN138" t="n">
         <v>0</v>
       </c>
+      <c r="AO138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -15100,6 +15406,9 @@
       <c r="AN139" t="n">
         <v>0</v>
       </c>
+      <c r="AO139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -15230,6 +15539,9 @@
         <v>0</v>
       </c>
       <c r="AN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO140" t="n">
         <v>0</v>
       </c>
     </row>
